--- a/outputs/botecs/uterotonics_pph_prevention.xlsx
+++ b/outputs/botecs/uterotonics_pph_prevention.xlsx
@@ -17,11 +17,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="164" formatCode="0.0%"/>
-    <numFmt numFmtId="165" formatCode="0.000%"/>
-    <numFmt numFmtId="166" formatCode="$#,##0.00"/>
-    <numFmt numFmtId="167" formatCode="$#,##0"/>
-    <numFmt numFmtId="168" formatCode="0.0"/>
+    <numFmt numFmtId="164" formatCode="$#,##0"/>
+    <numFmt numFmtId="165" formatCode="$#,##0.00"/>
+    <numFmt numFmtId="166" formatCode="0.0"/>
+    <numFmt numFmtId="167" formatCode="0.0%"/>
+    <numFmt numFmtId="168" formatCode="0.0000%"/>
   </numFmts>
   <fonts count="5">
     <font>
@@ -67,7 +67,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -75,19 +75,20 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -170,10 +171,42 @@
     <author>BOTEC</author>
   </authors>
   <commentList>
-    <comment ref="C2" authorId="0" shapeId="0">
+    <comment ref="C3" authorId="0" shapeId="0">
+      <text>
+        <t>Cost breakdown assumption:
+  HSC drug: $0.31 (Ferring subsidized price)
+  TXA drug (prorated): $3.00 x 6% PPH rate = $0.18
+  Training increment: ~$0.70 (short module for existing facility staff)
+  Supply chain: ~$0.35 (HSC is heat-stable; minimal cold chain)
+  Monitoring/supervision: ~$0.35
+Total: ~$1.89, rounded to $2.00.
+This assumes facilities and birth attendants already exist.
+For a standalone program (building facility capacity), costs would be much higher ($5-10/birth).</t>
+      </text>
+    </comment>
+    <comment ref="C7" authorId="0" shapeId="0">
+      <text>
+        <t>From PMC review: "prevent about 5,500 additional PPH cases and save five maternal lives per 100,000 births when priced comparably to oxytocin."
+https://pmc.ncbi.nlm.nih.gov/articles/PMC12145113/</t>
+      </text>
+    </comment>
+    <comment ref="C16" authorId="0" shapeId="0">
       <text>
         <t>WOMAN trial (2017): "Death due to bleeding was significantly reduced in women given tranexamic acid (155 [1.5%] of 10 036 patients vs 191 [1.9%] of 9985 in the placebo group, risk ratio [RR] 0.81, 95% CI 0.65-1.00; p=0.045)."
 http://www.thelancet.com/journals/lancet/article/PIIS0140-6736(17)30638-4/fulltext</t>
+      </text>
+    </comment>
+    <comment ref="C17" authorId="0" shapeId="0">
+      <text>
+        <t>2024 Lancet IPD meta-analysis (54,404 women, 5 RCTs): "Life-threatening bleeding occurred in 178 (0.65%) of 27,300 women in the tranexamic acid group versus 230 (0.85%) of 27,093 women in the placebo group (pooled odds ratio [OR] 0.77 [95% CI 0.63-0.93]; p=0.008)."
+Note: meta-analysis endpoint is composite (death + surgical interventions). WOMAN trial gives mortality-specific data; used as primary effect size.
+https://www.thelancet.com/journals/lancet/article/PIIS0140-6736(24)02102-0/fulltext</t>
+      </text>
+    </comment>
+    <comment ref="C38" authorId="0" shapeId="0">
+      <text>
+        <t>E-MOTIVE (Gallos et al., NEJM 2023): "A primary-outcome event occurred in 1.6% of the patients in the intervention group, as compared with 4.3% of those in the usual-care group (risk ratio, 0.40; 95% confidence interval [CI], 0.32 to 0.50; P&lt;0.001)." 210,132 women across 80 hospitals in Kenya, Nigeria, South Africa, and Tanzania.
+https://www.nejm.org/doi/full/10.1056/NEJMoa2303966</t>
       </text>
     </comment>
   </commentList>
@@ -469,10 +502,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="65" customWidth="1" min="1" max="1"/>
+    <col width="70" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="80" customWidth="1" min="3" max="3"/>
   </cols>
@@ -480,7 +513,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Section A: Tranexamic Acid (TXA) for PPH Treatment</t>
+          <t>Grant &amp; coverage</t>
         </is>
       </c>
       <c r="B1" s="2" t="inlineStr">
@@ -497,326 +530,504 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>PPH mortality rate with standard care (placebo arm)</t>
+          <t>Grant amount</t>
         </is>
       </c>
       <c r="B2" s="4" t="n">
-        <v>0.019</v>
+        <v>1000000</v>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>WOMAN trial: 191/9,985 = 1.91%</t>
+          <t>Arbitrary anchor for calculation</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Relative risk of death from bleeding with TXA vs placebo</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>0.8100000000000001</v>
+          <t>Cost per facility birth (bundled PPH program)</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="n">
+        <v>2</v>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>WOMAN trial RR 0.81 (95% CI 0.65-1.00). 2024 Lancet meta-analysis: 31% reduction within 3h.</t>
+          <t>I'm assuming $2/birth. Includes: HSC drug ($0.31), prorated TXA drug ($0.18), training increment ($0.70), supply chain ($0.35), monitoring ($0.35). Highly uncertain — at $1/birth CE roughly doubles; at $3/birth CE drops to ~2x. AMPLI-PPHI cost data (expected mid-2026) would resolve this.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Absolute risk reduction (deaths per PPH case treated)</t>
-        </is>
-      </c>
-      <c r="B4" s="6">
-        <f>B2*(1-B3)</f>
-        <v/>
-      </c>
-      <c r="C4" s="7" t="inlineStr">
-        <is>
-          <t>Calculation: mortality rate x (1 - RR)</t>
+          <t>Facility births covered by grant</t>
+        </is>
+      </c>
+      <c r="B4" s="7">
+        <f>B2/B3</f>
+        <v/>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>Calculation</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>TXA drug cost per patient (generic, LMIC)</t>
-        </is>
-      </c>
-      <c r="B5" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="C5" s="7" t="inlineStr">
-        <is>
-          <t>I'm estimating $1-5 for generic TXA (off-patent); $3 midpoint. Original used $17.48 (Guerriero 2011, Tanzania) which included hospital stay and nurse labor. Needs verification.</t>
-        </is>
-      </c>
+      <c r="C5" s="5" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Program cost multiplier (training, supply chain, monitoring)</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>10</v>
-      </c>
-      <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>I'm assuming 10x drug cost for program delivery. Highly uncertain. AMPLI-PPHI may have real data by 2026.</t>
-        </is>
-      </c>
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>HSC prevention: deaths averted</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total program cost per PPH case treated</t>
-        </is>
-      </c>
-      <c r="B7" s="9">
-        <f>B5*B6</f>
-        <v/>
-      </c>
-      <c r="C7" s="7" t="inlineStr">
-        <is>
-          <t>Calculation</t>
+          <t>Maternal lives saved per 100,000 facility births with HSC</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>India modeling study (2023), cited in PMC review. Compares HSC to settings without reliable uterotonic (cold-chain failure). I could not access the original study.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Cost per death averted — TXA</t>
-        </is>
-      </c>
-      <c r="B8" s="9">
-        <f>B7/B4</f>
-        <v/>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>Calculation</t>
+          <t>IV adjustment (HSC)</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Modeling study, not direct RCT in the target setting. Based on CHAMPION trial (HSC non-inferior to oxytocin) plus assumptions about cold-chain failure rates.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>GiveDirectly benchmark (cost per death averted equivalent)</t>
+          <t>EV adjustment (HSC)</t>
         </is>
       </c>
       <c r="B9" s="9" t="n">
-        <v>4500</v>
-      </c>
-      <c r="C9" s="7" t="inlineStr">
-        <is>
-          <t>I'm assuming ~$4,500. Exact figure depends on GW moral weights and year. Needs verification.</t>
+        <v>0.9</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>India model applied to broader LMIC settings. Cold-chain reliability varies across settings.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CE — TXA (multiples of cash)</t>
+          <t>Adjusted lives saved per 100,000 births</t>
         </is>
       </c>
       <c r="B10" s="10">
-        <f>B9/B8</f>
-        <v/>
-      </c>
-      <c r="C10" s="7" t="inlineStr">
-        <is>
-          <t>Low because TXA only reduces mortality among women who already have PPH; per-case impact is small.</t>
+        <f>B7*B8*B9</f>
+        <v/>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Calculation</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="C11" s="7" t="n"/>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Deaths averted from HSC</t>
+        </is>
+      </c>
+      <c r="B11" s="11">
+        <f>B4/100000*B10</f>
+        <v/>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Calculation</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Section B: Heat-Stable Carbetocin (HSC) for PPH Prevention</t>
-        </is>
-      </c>
-      <c r="C12" s="7" t="n"/>
+      <c r="C12" s="5" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>HSC drug cost per birth (LMIC public sector)</t>
-        </is>
-      </c>
-      <c r="B13" s="8" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>Ferring subsidized price: $0.31/ampoule</t>
-        </is>
-      </c>
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>TXA treatment: deaths averted</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Facility births per 100,000 total births (estimate)</t>
-        </is>
-      </c>
-      <c r="B14" s="11" t="n">
-        <v>100000</v>
-      </c>
-      <c r="C14" s="7" t="inlineStr">
-        <is>
-          <t>Modeling per 100,000 facility births (consistent with source)</t>
+          <t>PPH rate among facility births</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>~6% is standard WHO estimate for PPH incidence (blood loss &gt;= 500ml after birth).</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Maternal lives saved per 100,000 facility births with HSC</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>5</v>
+          <t>PPH cases from grant</t>
+        </is>
+      </c>
+      <c r="B15" s="7">
+        <f>B4*B14</f>
+        <v/>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>India modeling study (2023), cited in PMC review. I could not access the original study.</t>
+          <t>Calculation</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Drug cost per life saved — HSC</t>
-        </is>
-      </c>
-      <c r="B16" s="9">
-        <f>B13*B14/B15</f>
-        <v/>
-      </c>
-      <c r="C16" s="7" t="inlineStr">
-        <is>
-          <t>Calculation: drug cost x births / lives saved</t>
+          <t>Mortality rate among PPH cases (standard care)</t>
+        </is>
+      </c>
+      <c r="B16" s="12" t="n">
+        <v>0.019</v>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>WOMAN trial placebo arm: 191/9,985 = 1.91%</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Program cost multiplier (HSC)</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>20</v>
-      </c>
-      <c r="C17" s="7" t="inlineStr">
-        <is>
-          <t>I'm assuming 20x drug cost for full program. HSC requires facility delivery and cold-chain-free storage. Highly uncertain.</t>
+          <t>Relative risk reduction from TXA (1 - RR)</t>
+        </is>
+      </c>
+      <c r="B17" s="9" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>WOMAN trial: RR 0.81 (95% CI 0.65-1.00) for death from bleeding. Using WOMAN trial as primary source for mortality. 2024 Lancet IPD meta-analysis (OR 0.77 for life-threatening bleeding composite) is confirmatory.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Full program cost per life saved — HSC</t>
-        </is>
-      </c>
-      <c r="B18" s="9">
-        <f>B16*B17</f>
-        <v/>
-      </c>
-      <c r="C18" s="7" t="inlineStr">
-        <is>
-          <t>Calculation</t>
+          <t>IV adjustment (TXA)</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>Large, high-quality multi-country RCT (WOMAN trial). Confirmed by 2024 IPD meta-analysis. Small discount for field vs. trial conditions.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CE — HSC (multiples of cash)</t>
-        </is>
-      </c>
-      <c r="B19" s="12">
-        <f>B9/B18</f>
-        <v/>
-      </c>
-      <c r="C19" s="7" t="inlineStr">
-        <is>
-          <t>Uses same GiveDirectly benchmark as Section A</t>
+          <t>EV adjustment (TXA)</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>WOMAN trial included LMIC sites, but TXA requires rapid PPH diagnosis and IV/IM administration within 3 hours. Effectiveness in field conditions may be lower than trial.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="C20" s="7" t="n"/>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Adjusted deaths averted per PPH case treated</t>
+        </is>
+      </c>
+      <c r="B20" s="13">
+        <f>B16*B17*B18*B19</f>
+        <v/>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>Calculation: CFR x RRR x IV x EV</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>Combined estimate</t>
-        </is>
-      </c>
-      <c r="C21" s="7" t="n"/>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Deaths averted from TXA</t>
+        </is>
+      </c>
+      <c r="B21" s="11">
+        <f>B15*B20</f>
+        <v/>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>Calculation</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Bundled PPH program CE estimate (judgment)</t>
-        </is>
-      </c>
-      <c r="B22" s="13" t="inlineStr">
-        <is>
-          <t>8-15x</t>
-        </is>
-      </c>
-      <c r="C22" s="7" t="inlineStr">
-        <is>
-          <t>The per-product estimates above are lower than this because a bundled program shares fixed costs (training, supply chain, facility infrastructure) across TXA + HSC + monitoring. 8-15x is my judgment call for a well-run bundled program. Confidence: Low.</t>
-        </is>
-      </c>
+      <c r="C22" s="5" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Key driver of uncertainty</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Program costs</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>AMPLI-PPHI ($26M, 6 countries) should have real cost data by mid-2026</t>
-        </is>
-      </c>
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>Total benefits</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Note: misoprostol is off the table</t>
-        </is>
+          <t>Total deaths averted (HSC + TXA)</t>
+        </is>
+      </c>
+      <c r="B24" s="11">
+        <f>B11+B21</f>
+        <v/>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
+          <t>Calculation. Slight overcount: HSC prevents some PPH, reducing TXA treatment pool. Effect is small (~10%).</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>UoV per maternal death averted (GW moral weights)</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>GiveWell standard moral weight for LMIC adult death. Maternal deaths are women aged 15-49.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>UoV from mortality</t>
+        </is>
+      </c>
+      <c r="B26" s="7">
+        <f>B24*B25</f>
+        <v/>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>Calculation</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Morbidity uplift (% of mortality UoV)</t>
+        </is>
+      </c>
+      <c r="B27" s="9" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>I'm assuming +75%. PPH causes severe anemia, need for blood transfusion, surgical interventions (hysterectomy, laparotomy), and long-term disability. For every PPH death, many women survive with significant morbidity. Rough guess.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Treatment costs averted uplift (% of mortality UoV)</t>
+        </is>
+      </c>
+      <c r="B28" s="9" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>I'm assuming +25%. Blood transfusions are scarce and expensive in LMICs; surgical interventions carry high cost. Rough guess.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Total UoV from grant</t>
+        </is>
+      </c>
+      <c r="B29" s="7">
+        <f>B26*(1+B27+B28)</f>
+        <v/>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>Calculation: mortality UoV x (1 + morbidity + treatment)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="C30" s="5" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>Final CE estimate</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>UoV per $100,000 donated</t>
+        </is>
+      </c>
+      <c r="B32" s="7">
+        <f>B29/B2*100000</f>
+        <v/>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>Calculation</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>GiveDirectly units of value per $100,000</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>344</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>GW benchmark (1x cash transfers)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Cost per death averted</t>
+        </is>
+      </c>
+      <c r="B34" s="4">
+        <f>B2/B24</f>
+        <v/>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>Calculation (mortality only; morbidity benefits additional)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>CE (multiples of cash)</t>
+        </is>
+      </c>
+      <c r="B35" s="14">
+        <f>B32/B33</f>
+        <v/>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>Best-guess estimate. Highly sensitive to cost/birth: at $1/birth -&gt; ~6.5x; at $3/birth -&gt; ~2.2x. Confidence: Low.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="C36" s="5" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>Context &amp; notes</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>E-MOTIVE trial (bundled detection + treatment)</t>
+        </is>
+      </c>
+      <c r="C38" s="8" t="inlineStr">
+        <is>
+          <t>NEJM 2023: bundled PPH early detection + treatment reduced composite outcome (severe PPH, laparotomy, or death) by 60% (RR 0.40, 95% CI 0.32-0.50). Supports the bundled approach modeled above but uses a different intervention package.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Misoprostol: off the table</t>
+        </is>
+      </c>
+      <c r="C39" s="8" t="inlineStr">
+        <is>
           <t>WHO 2025: misoprostol is 'last resort' when no injectable options are available</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Key cost data source</t>
+        </is>
+      </c>
+      <c r="C40" s="8" t="inlineStr">
+        <is>
+          <t>AMPLI-PPHI ($26M, 6 countries, 2022-2026) is generating cost-effectiveness evidence. Results expected by mid-2026.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C23" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C24" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C17" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C38" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C39" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C40" r:id="rId6"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
